--- a/rules/sources/sec.nport.registrant/MAPPING.xlsx
+++ b/rules/sources/sec.nport.registrant/MAPPING.xlsx
@@ -1210,7 +1210,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rules/sources/sec.nport.registrant/MAPPING.xlsx
+++ b/rules/sources/sec.nport.registrant/MAPPING.xlsx
@@ -13,7 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Critical data elements" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data quality" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Who wins" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline targets" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline steps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1163,6 +1165,471 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="51" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Run checks</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Lease seconds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Heartbeat seconds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>manifest.hash, work.accounting, journal.delivered</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Requires</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>submissions</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>filings</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>submissions</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ciks</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>source.combine</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>filings</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.combined</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>combine</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>source.combine</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ciks, filings</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.combined</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>combine</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>prepare</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>mdm.prepare</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, mdm.prepared</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>mdm.merge</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>prepare</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>{batch_id}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>mdm:consumer:{consumer}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, mdm.committed</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>processed</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>journal.record</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, journal.recorded</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[7]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
